--- a/documentation/scrum/Sprint_1_Burndown_Chart.xlsx
+++ b/documentation/scrum/Sprint_1_Burndown_Chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://micloud365-my.sharepoint.com/personal/imashai_millenniumitesp_com/Documents/Desktop/MSc BInA/Academics/3-Interactive Visualization/Assesment/Project/group4-interactive-visualisation/documentation/scrum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="11_2C750128247682E81B996B25C37309B4575122DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F62A7CD0-3559-4AED-81D6-261419FF3214}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="11_2C750128247682E81B996B25C37309B4575122DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCAB2B0D-CEED-4EEF-BF23-1F49212564BA}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="96">
   <si>
     <t>Day</t>
   </si>
@@ -61,15 +61,9 @@
     <t>Day 0</t>
   </si>
   <si>
-    <t>Sprint starts; 20 checklist items planned.</t>
-  </si>
-  <si>
     <t>Day 1</t>
   </si>
   <si>
-    <t>Enter actual remaining items from Trello.</t>
-  </si>
-  <si>
     <t>Day 2</t>
   </si>
   <si>
@@ -82,9 +76,6 @@
     <t>Day 5</t>
   </si>
   <si>
-    <t>Sprint end; enter actual remaining items from Trello.</t>
-  </si>
-  <si>
     <t>ID</t>
   </si>
   <si>
@@ -314,6 +305,27 @@
   </si>
   <si>
     <t>Day Number</t>
+  </si>
+  <si>
+    <t>Sprint 1 starts; 20 checklist items planned. Review assessment requirements, Select project topic, Select dataset, Identify target audience, and Define overarching research question (S1-01 to S1-05) closed today, per actual Trello count.</t>
+  </si>
+  <si>
+    <t>Define Chart 1, Chart 2, and Chart 3 research questions (S1-06 to S1-08) closed today, per actual Trello count.</t>
+  </si>
+  <si>
+    <t>Select Chart 1, Chart 2, and Chart 3 types (S1-09 to S1-11) closed today, per actual Trello count.</t>
+  </si>
+  <si>
+    <t>Create Trello board and add team members (S1-12, S1-13) closed today, per actual Trello count.</t>
+  </si>
+  <si>
+    <t>Create GitHub repository, add team members to GitHub, and create GitHub folder structure (S1-14 to S1-16) closed today, per actual Trello count.</t>
+  </si>
+  <si>
+    <t>Initial dataset analysis and identify missing/duplicate data (S1-17, S1-18) closed today, per actual Trello count.</t>
+  </si>
+  <si>
+    <t>Sprint end. Prepare Meeting 01 minutes and Prepare Sprint 1 documentation (S1-19, S1-20) .</t>
   </si>
 </sst>
 </file>
@@ -408,10 +420,10 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr/>
+              <a:defRPr sz="1800"/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
+              <a:rPr lang="en-US" sz="1800"/>
               <a:t>Sprint 1 Burndown Chart</a:t>
             </a:r>
           </a:p>
@@ -421,7 +433,17 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.262715471376889E-2"/>
+          <c:y val="0.1644601527081842"/>
+          <c:w val="0.70177063972153708"/>
+          <c:h val="0.78324504891434021"/>
+        </c:manualLayout>
+      </c:layout>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="1"/>
@@ -686,6 +708,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.75699469433273647"/>
+          <c:y val="0.43150411596277738"/>
+          <c:w val="0.23012976918657699"/>
+          <c:h val="0.17108267716535433"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="1"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
@@ -704,12 +736,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>146050</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5400000" cy="2880000"/>
+    <xdr:ext cx="7518400" cy="3352800"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -1033,7 +1065,7 @@
     <col min="3" max="3" width="20" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="50" customWidth="1"/>
+    <col min="6" max="6" width="197.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
@@ -1073,12 +1105,12 @@
         <v>5</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>7</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" s="4">
         <v>46286</v>
@@ -1093,12 +1125,12 @@
         <v>3</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>9</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" s="4">
         <v>46287</v>
@@ -1110,16 +1142,16 @@
         <v>9</v>
       </c>
       <c r="E4" s="2">
-        <f t="shared" ref="E3:E9" si="0">IF(OR(D4="",D3=""),"",D3-D4)</f>
+        <f t="shared" ref="E4:E9" si="0">IF(OR(D4="",D3=""),"",D3-D4)</f>
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>9</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" s="4">
         <v>46288</v>
@@ -1135,12 +1167,12 @@
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" s="4">
         <v>46289</v>
@@ -1156,12 +1188,12 @@
         <v>3</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>9</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" s="4">
         <v>46290</v>
@@ -1177,12 +1209,12 @@
         <v>2</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>9</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B8" s="4">
         <v>46291</v>
@@ -1198,7 +1230,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>14</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -1235,51 +1267,51 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="G1" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1287,25 +1319,25 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1313,25 +1345,25 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1339,25 +1371,25 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1365,25 +1397,25 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1391,25 +1423,25 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1417,25 +1449,25 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G8" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -1443,25 +1475,25 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1469,25 +1501,25 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G10" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -1495,25 +1527,25 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" t="s">
         <v>43</v>
       </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -1521,25 +1553,25 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G12" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="H12">
         <v>2</v>
@@ -1547,25 +1579,25 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B13" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H13">
         <v>3</v>
@@ -1573,25 +1605,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" t="s">
         <v>50</v>
       </c>
-      <c r="C14" t="s">
-        <v>53</v>
-      </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E14" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H14">
         <v>3</v>
@@ -1599,25 +1631,25 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E15" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H15">
         <v>4</v>
@@ -1625,25 +1657,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E16" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F16" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H16">
         <v>4</v>
@@ -1651,25 +1683,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F17" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H17">
         <v>4</v>
@@ -1677,25 +1709,25 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C18" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="D18" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G18" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H18">
         <v>5</v>
@@ -1703,25 +1735,25 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" t="s">
         <v>61</v>
       </c>
-      <c r="C19" t="s">
-        <v>64</v>
-      </c>
       <c r="D19" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="H19">
         <v>5</v>
@@ -1729,25 +1761,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E20" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G20" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H20">
         <v>6</v>
@@ -1755,25 +1787,25 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" t="s">
         <v>66</v>
       </c>
-      <c r="C21" t="s">
-        <v>69</v>
-      </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G21" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="H21">
         <v>6</v>
@@ -1796,34 +1828,34 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -1831,31 +1863,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/scrum/Sprint_1_Burndown_Chart.xlsx
+++ b/documentation/scrum/Sprint_1_Burndown_Chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://micloud365-my.sharepoint.com/personal/imashai_millenniumitesp_com/Documents/Desktop/MSc BInA/Academics/3-Interactive Visualization/Assesment/Project/group4-interactive-visualisation/documentation/scrum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="11_2C750128247682E81B996B25C37309B4575122DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCAB2B0D-CEED-4EEF-BF23-1F49212564BA}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="11_2C750128247682E81B996B25C37309B4575122DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61AECF1C-F1B8-4178-8CEE-61A0AFC791A8}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,9 @@
     <sheet name="Task Register" sheetId="2" r:id="rId2"/>
     <sheet name="Instructions" sheetId="3" r:id="rId3"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Task Register'!$A$1:$F$21</definedName>
   </definedNames>
@@ -38,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="98">
   <si>
     <t>Day</t>
   </si>
@@ -326,13 +329,19 @@
   </si>
   <si>
     <t>Sprint end. Prepare Meeting 01 minutes and Prepare Sprint 1 documentation (S1-19, S1-20) .</t>
+  </si>
+  <si>
+    <t>Day 0 starting point</t>
+  </si>
+  <si>
+    <t>Day 0 (20 Sep 2026) is the Sprint 1 kickoff, when all 20 checklist items (S1-01 to S1-20) were open. Five planning items were closed on Day 0 per the actual Trello count (S1-01 to S1-05: review assessment requirements, select project topic, select dataset, identify target audience, define overarching research question), leaving 15 items open at the end of Day 0.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -350,6 +359,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -377,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -388,6 +402,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -410,7 +430,7 @@
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
-  <c:roundedCorners val="1"/>
+  <c:roundedCorners val="0"/>
   <c:style val="2"/>
   <c:chart>
     <c:title>
@@ -438,14 +458,14 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="3.262715471376889E-2"/>
+          <c:x val="8.6006464141306666E-2"/>
           <c:y val="0.1644601527081842"/>
-          <c:w val="0.70177063972153708"/>
-          <c:h val="0.78324504891434021"/>
+          <c:w val="0.65109491381144913"/>
+          <c:h val="0.70801002147458836"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
-        <c:grouping val="standard"/>
+        <c:grouping val="stacked"/>
         <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
@@ -640,7 +660,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="b"/>
         <c:title>
           <c:tx>
@@ -661,7 +681,7 @@
           <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="100"/>
@@ -676,7 +696,7 @@
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
-        <c:delete val="1"/>
+        <c:delete val="0"/>
         <c:axPos val="l"/>
         <c:majorGridlines/>
         <c:title>
@@ -695,16 +715,30 @@
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="1.654554160459672E-2"/>
+              <c:y val="0.33833631591505609"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="1"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="10"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="25400">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
@@ -714,8 +748,8 @@
           <c:yMode val="edge"/>
           <c:x val="0.75699469433273647"/>
           <c:y val="0.43150411596277738"/>
-          <c:w val="0.23012976918657699"/>
-          <c:h val="0.17108267716535433"/>
+          <c:w val="0.188408133056475"/>
+          <c:h val="0.11337249771678226"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="1"/>
@@ -724,6 +758,15 @@
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:spPr>
+    <a:ln w="3175">
+      <a:solidFill>
+        <a:schemeClr val="bg1">
+          <a:lumMod val="75000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
@@ -741,7 +784,7 @@
       <xdr:row>10</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7518400" cy="3352800"/>
+    <xdr:ext cx="7296150" cy="4051300"/>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1">
@@ -768,8 +811,110 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sprint 2 Burndown"/>
+      <sheetName val="Task Register"/>
+      <sheetName val="Instructions"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="1">
+          <cell r="C1" t="str">
+            <v>Planned Remaining</v>
+          </cell>
+          <cell r="D1" t="str">
+            <v>Actual Remaining</v>
+          </cell>
+        </row>
+        <row r="2">
+          <cell r="A2" t="str">
+            <v>Day 0</v>
+          </cell>
+          <cell r="C2">
+            <v>19</v>
+          </cell>
+          <cell r="D2">
+            <v>7</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="A3" t="str">
+            <v>Day 1</v>
+          </cell>
+          <cell r="C3">
+            <v>16</v>
+          </cell>
+          <cell r="D3">
+            <v>6</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="A4" t="str">
+            <v>Day 2</v>
+          </cell>
+          <cell r="C4">
+            <v>13</v>
+          </cell>
+          <cell r="D4">
+            <v>5</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="A5" t="str">
+            <v>Day 3</v>
+          </cell>
+          <cell r="C5">
+            <v>10</v>
+          </cell>
+          <cell r="D5">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="A6" t="str">
+            <v>Day 4</v>
+          </cell>
+          <cell r="C6">
+            <v>6</v>
+          </cell>
+          <cell r="D6">
+            <v>2</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="A7" t="str">
+            <v>Day 5</v>
+          </cell>
+          <cell r="C7">
+            <v>3</v>
+          </cell>
+          <cell r="D7">
+            <v>1</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="A8" t="str">
+            <v>Day 6</v>
+          </cell>
+          <cell r="C8">
+            <v>0</v>
+          </cell>
+          <cell r="D8">
+            <v>0</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1819,7 +1964,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1850,43 +1995,51 @@
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B5" s="2" t="s">
         <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>76</v>
+        <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>81</v>
       </c>
     </row>

--- a/documentation/scrum/Sprint_1_Burndown_Chart.xlsx
+++ b/documentation/scrum/Sprint_1_Burndown_Chart.xlsx
@@ -8,18 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://micloud365-my.sharepoint.com/personal/imashai_millenniumitesp_com/Documents/Desktop/MSc BInA/Academics/3-Interactive Visualization/Assesment/Project/group4-interactive-visualisation/documentation/scrum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="11_2C750128247682E81B996B25C37309B4575122DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61AECF1C-F1B8-4178-8CEE-61A0AFC791A8}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="11_2C750128247682E81B996B25C37309B4575122DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{043D8B29-3842-4146-9703-991A40BF1701}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="380" windowWidth="19200" windowHeight="11280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 1 Burndown" sheetId="1" r:id="rId1"/>
     <sheet name="Task Register" sheetId="2" r:id="rId2"/>
     <sheet name="Instructions" sheetId="3" r:id="rId3"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Task Register'!$A$1:$F$21</definedName>
   </definedNames>
@@ -112,9 +109,6 @@
     <t>To Do</t>
   </si>
   <si>
-    <t>No</t>
-  </si>
-  <si>
     <t>S1-02</t>
   </si>
   <si>
@@ -335,6 +329,9 @@
   </si>
   <si>
     <t>Day 0 (20 Sep 2026) is the Sprint 1 kickoff, when all 20 checklist items (S1-01 to S1-20) were open. Five planning items were closed on Day 0 per the actual Trello count (S1-01 to S1-05: review assessment requirements, select project topic, select dataset, identify target audience, define overarching research question), leaving 15 items open at the end of Day 0.</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -811,110 +808,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Sprint 2 Burndown"/>
-      <sheetName val="Task Register"/>
-      <sheetName val="Instructions"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="C1" t="str">
-            <v>Planned Remaining</v>
-          </cell>
-          <cell r="D1" t="str">
-            <v>Actual Remaining</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>Day 0</v>
-          </cell>
-          <cell r="C2">
-            <v>19</v>
-          </cell>
-          <cell r="D2">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>Day 1</v>
-          </cell>
-          <cell r="C3">
-            <v>16</v>
-          </cell>
-          <cell r="D3">
-            <v>6</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>Day 2</v>
-          </cell>
-          <cell r="C4">
-            <v>13</v>
-          </cell>
-          <cell r="D4">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>Day 3</v>
-          </cell>
-          <cell r="C5">
-            <v>10</v>
-          </cell>
-          <cell r="D5">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>Day 4</v>
-          </cell>
-          <cell r="C6">
-            <v>6</v>
-          </cell>
-          <cell r="D6">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>Day 5</v>
-          </cell>
-          <cell r="C7">
-            <v>3</v>
-          </cell>
-          <cell r="D7">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>Day 6</v>
-          </cell>
-          <cell r="C8">
-            <v>0</v>
-          </cell>
-          <cell r="D8">
-            <v>0</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1250,7 +1145,7 @@
         <v>5</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -1270,7 +1165,7 @@
         <v>3</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -1291,7 +1186,7 @@
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -1312,7 +1207,7 @@
         <v>2</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -1333,7 +1228,7 @@
         <v>3</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -1354,12 +1249,12 @@
         <v>2</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B8" s="4">
         <v>46291</v>
@@ -1375,7 +1270,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -1430,10 +1325,10 @@
         <v>17</v>
       </c>
       <c r="G1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -1453,10 +1348,10 @@
         <v>22</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1464,13 +1359,13 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
         <v>21</v>
@@ -1479,10 +1374,10 @@
         <v>22</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -1490,13 +1385,13 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
@@ -1505,10 +1400,10 @@
         <v>22</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -1516,25 +1411,25 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
       <c r="C5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" t="s">
         <v>29</v>
-      </c>
-      <c r="D5" t="s">
-        <v>30</v>
       </c>
       <c r="E5" t="s">
         <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1542,13 +1437,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
         <v>21</v>
@@ -1557,10 +1452,10 @@
         <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H6">
         <v>0</v>
@@ -1568,13 +1463,13 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
         <v>21</v>
@@ -1583,10 +1478,10 @@
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -1594,13 +1489,13 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
         <v>21</v>
@@ -1609,10 +1504,10 @@
         <v>22</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -1620,13 +1515,13 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
         <v>21</v>
@@ -1635,10 +1530,10 @@
         <v>22</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -1646,13 +1541,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
         <v>39</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>40</v>
-      </c>
-      <c r="C10" t="s">
-        <v>41</v>
       </c>
       <c r="D10" t="s">
         <v>21</v>
@@ -1661,10 +1556,10 @@
         <v>22</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -1672,13 +1567,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
         <v>42</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" t="s">
-        <v>43</v>
       </c>
       <c r="D11" t="s">
         <v>21</v>
@@ -1687,10 +1582,10 @@
         <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H11">
         <v>2</v>
@@ -1698,13 +1593,13 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
         <v>44</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
       </c>
       <c r="D12" t="s">
         <v>21</v>
@@ -1713,10 +1608,10 @@
         <v>22</v>
       </c>
       <c r="F12" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H12">
         <v>2</v>
@@ -1724,13 +1619,13 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" t="s">
         <v>46</v>
       </c>
-      <c r="B13" t="s">
+      <c r="C13" t="s">
         <v>47</v>
-      </c>
-      <c r="C13" t="s">
-        <v>48</v>
       </c>
       <c r="D13" t="s">
         <v>21</v>
@@ -1739,10 +1634,10 @@
         <v>22</v>
       </c>
       <c r="F13" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H13">
         <v>3</v>
@@ -1750,25 +1645,25 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" t="s">
         <v>49</v>
       </c>
-      <c r="B14" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
       <c r="D14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
         <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H14">
         <v>3</v>
@@ -1776,13 +1671,13 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" t="s">
         <v>51</v>
-      </c>
-      <c r="B15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C15" t="s">
-        <v>52</v>
       </c>
       <c r="D15" t="s">
         <v>21</v>
@@ -1791,10 +1686,10 @@
         <v>22</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H15">
         <v>4</v>
@@ -1802,25 +1697,25 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
         <v>53</v>
       </c>
-      <c r="B16" t="s">
-        <v>47</v>
-      </c>
-      <c r="C16" t="s">
-        <v>54</v>
-      </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s">
         <v>22</v>
       </c>
       <c r="F16" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H16">
         <v>4</v>
@@ -1828,25 +1723,25 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" t="s">
         <v>55</v>
       </c>
-      <c r="B17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C17" t="s">
-        <v>56</v>
-      </c>
       <c r="D17" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
         <v>22</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H17">
         <v>4</v>
@@ -1854,13 +1749,13 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B18" t="s">
         <v>57</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>58</v>
-      </c>
-      <c r="C18" t="s">
-        <v>59</v>
       </c>
       <c r="D18" t="s">
         <v>21</v>
@@ -1869,10 +1764,10 @@
         <v>22</v>
       </c>
       <c r="F18" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H18">
         <v>5</v>
@@ -1880,13 +1775,13 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s">
         <v>60</v>
-      </c>
-      <c r="B19" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" t="s">
-        <v>61</v>
       </c>
       <c r="D19" t="s">
         <v>21</v>
@@ -1895,10 +1790,10 @@
         <v>22</v>
       </c>
       <c r="F19" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G19" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="H19">
         <v>5</v>
@@ -1906,25 +1801,25 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20" t="s">
         <v>62</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>63</v>
       </c>
-      <c r="C20" t="s">
-        <v>64</v>
-      </c>
       <c r="D20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E20" t="s">
         <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H20">
         <v>6</v>
@@ -1932,25 +1827,25 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>64</v>
+      </c>
+      <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
         <v>65</v>
       </c>
-      <c r="B21" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" t="s">
-        <v>66</v>
-      </c>
       <c r="D21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E21" t="s">
         <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>23</v>
+        <v>97</v>
       </c>
       <c r="G21" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H21">
         <v>6</v>
@@ -1973,42 +1868,42 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -2016,31 +1911,31 @@
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/scrum/Sprint_1_Burndown_Chart.xlsx
+++ b/documentation/scrum/Sprint_1_Burndown_Chart.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://micloud365-my.sharepoint.com/personal/imashai_millenniumitesp_com/Documents/Desktop/MSc BInA/Academics/3-Interactive Visualization/Assesment/Project/group4-interactive-visualisation/documentation/scrum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="124" documentId="11_2C750128247682E81B996B25C37309B4575122DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{043D8B29-3842-4146-9703-991A40BF1701}"/>
+  <xr:revisionPtr revIDLastSave="126" documentId="11_2C750128247682E81B996B25C37309B4575122DD" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D47A1D3-C78E-49E7-A697-C95D706B30D1}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="380" windowWidth="19200" windowHeight="11280" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprint 1 Burndown" sheetId="1" r:id="rId1"/>
@@ -1859,7 +1859,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -1938,6 +1938,9 @@
         <v>80</v>
       </c>
     </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
